--- a/REVIEWED_mayor_bronson_20210728_20240119_20260513_autoPush.xlsx
+++ b/REVIEWED_mayor_bronson_20210728_20240119_20260513_autoPush.xlsx
@@ -46850,7 +46850,7 @@
         <v>0</v>
       </c>
       <c r="M908" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N908" t="inlineStr"/>
     </row>
